--- a/data/manufacturing/RAGFlow_크랭크샤프트_가공_오류DB.xlsx
+++ b/data/manufacturing/RAGFlow_크랭크샤프트_가공_오류DB.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="오류주의사항DB" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="오류주의사항DB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="출처" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'오류주의사항DB'!$A$1:$AA$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'오류주의사항DB'!$A$1:$AA$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5169,8 +5169,1346 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="120" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CS-M-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>크랭크샤프트</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Ø680(+0.08/0)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>[황삭] 크랭크핀 공차 (+0.08/0)을 축이니 − 공차라고 착각해 679.98을 합격 처리</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀 Ø680(+0.08/0)은 680.000~680.080만 합격인데, '축은 보통 − 공차'라고 생각해 679.980을 합격으로 기록했다. 이 도면의 핀 공차는 + 방향이다.</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>공차 방향 선입견</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>축·구멍 여부와 관계없이 도면 괄호 안 값 그대로 허용 범위를 계산한다. 화면의 허용 범위(최소~최대)를 숫자로 확인하고 판정한다.</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>대형 외측 마이크로미터, 기준봉</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>크랭크스로 단품 가공에서 마무리하는 크랭크핀</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>도면 해석</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>황삭 후</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>커넥팅로드 대단부와 틈새 과대, 베어링 손상</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>허용 범위로 재판정, 재가공 여부 결정</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 크랭크핀, 외경, DIMENSION, Ø680(+0.08/0), 공차 방향 선입견, 크랭크핀, C3 도면 해석, 황삭 후</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CS-M-035] 부품: 크랭크샤프트. 부위: 크랭크핀. 형상: 크랭크핀(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø680(+0.08/0). 오류 유형: C3 도면 해석. 중요도: 상. 오류: [황삭] 크랭크핀 공차 (+0.08/0)을 축이니 − 공차라고 착각해 679.98을 합격 처리. 상황: 크랭크핀 Ø680(+0.08/0)은 680.000~680.080만 합격인데, '축은 보통 − 공차'라고 생각해 679.980을 합격으로 기록했다. 이 도면의 핀 공차는 + 방향이다. 원인: 공차 방향 선입견. 주의사항: 축·구멍 여부와 관계없이 도면 괄호 안 값 그대로 허용 범위를 계산한다. 화면의 허용 범위(최소~최대)를 숫자로 확인하고 판정한다. 조치: 허용 범위로 재판정, 재가공 여부 결정. 영향: 커넥팅로드 대단부와 틈새 과대, 베어링 손상. 발생 단계: 황삭 후. 적용 조건: 크랭크스로 단품 가공에서 마무리하는 크랭크핀. 제외·확인 조건: 없음. 측정기 후보: 대형 외측 마이크로미터, 기준봉. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="120" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CS-M-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>크랭크샤프트</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Ø680(+0.08/0)</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>[황삭] 크랭크핀 마무리 직후 따뜻한 상태로 끼워맞춤 공차 판정</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>크랭크스로 단품에서 핀을 마무리한 직후 표면이 측정실보다 4℃ 높은 상태에서 680.070(합격)으로 기록했다. 강은 Ø680에서 4℃당 약 0.031mm 커지므로 식은 뒤 실제 값은 680.039 근처다. 공차 폭 0.08mm의 약 40%가 온도로 움직인다.</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤면 온도 보정 누락</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤 핀은 표면 온도를 함께 기록하고, 측정실과 2℃ 이상 차이 나면 식힌 뒤 다시 잰다. 기준봉도 같은 온도에 둔다.</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>대형 외측 마이크로미터, 표면 온도계</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>가공 직후 끼워맞춤 핀</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>온도 안정 후 측정한 경우 제외</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>온도·환경</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>황삭 후</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>성적서 값과 실제 치수 차이</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>온도 안정 후 재측정</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 크랭크핀, 외경, DIMENSION, Ø680(+0.08/0), 끼워맞춤면 온도 보정 누락, 크랭크핀, C9 온도·환경, 황삭 후</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CS-M-036] 부품: 크랭크샤프트. 부위: 크랭크핀. 형상: 크랭크핀(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø680(+0.08/0). 오류 유형: C9 온도·환경. 중요도: 중. 오류: [황삭] 크랭크핀 마무리 직후 따뜻한 상태로 끼워맞춤 공차 판정. 상황: 크랭크스로 단품에서 핀을 마무리한 직후 표면이 측정실보다 4℃ 높은 상태에서 680.070(합격)으로 기록했다. 강은 Ø680에서 4℃당 약 0.031mm 커지므로 식은 뒤 실제 값은 680.039 근처다. 공차 폭 0.08mm의 약 40%가 온도로 움직인다. 원인: 끼워맞춤면 온도 보정 누락. 주의사항: 끼워맞춤 핀은 표면 온도를 함께 기록하고, 측정실과 2℃ 이상 차이 나면 식힌 뒤 다시 잰다. 기준봉도 같은 온도에 둔다. 조치: 온도 안정 후 재측정. 영향: 성적서 값과 실제 치수 차이. 발생 단계: 황삭 후. 적용 조건: 가공 직후 끼워맞춤 핀. 제외·확인 조건: 온도 안정 후 측정한 경우 제외. 측정기 후보: 대형 외측 마이크로미터, 표면 온도계. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="120" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CS-M-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>크랭크샤프트</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Ø680(+0.08/0)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>[황삭] 웨브 사이가 좁아 마이크로미터를 비스듬히 대서 핀 지름 과대</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀 양쪽 웨브 사이가 좁아 대형 마이크로미터를 축에 직각으로 대지 못하고 비스듬히 대서 680.090(불합격)으로 기록했다. 직각으로 다시 대니 680.055였다.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>측정기 자세 불량 (경사 오차)</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>마이크로미터는 축에 직각으로 대고 축 방향으로 조금씩 흔들어 최소값을 읽는다. 공간이 좁으면 핀 전용 게이지(스냅 게이지)나 짧은 프레임을 쓴다.</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>대형 외측 마이크로미터, 핀 게이지</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>웨브 사이 크랭크핀 측정</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>측정 방법</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>황삭 후</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>불필요한 재가공 또는 오판정</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>자세 교정 후 재측정</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 크랭크핀, 외경, DIMENSION, Ø680(+0.08/0), 측정기 자세 불량 (경사 오차), 크랭크핀, C5 측정 방법, 황삭 후</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CS-M-037] 부품: 크랭크샤프트. 부위: 크랭크핀. 형상: 크랭크핀(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø680(+0.08/0). 오류 유형: C5 측정 방법. 중요도: 중. 오류: [황삭] 웨브 사이가 좁아 마이크로미터를 비스듬히 대서 핀 지름 과대. 상황: 크랭크핀 양쪽 웨브 사이가 좁아 대형 마이크로미터를 축에 직각으로 대지 못하고 비스듬히 대서 680.090(불합격)으로 기록했다. 직각으로 다시 대니 680.055였다. 원인: 측정기 자세 불량 (경사 오차). 주의사항: 마이크로미터는 축에 직각으로 대고 축 방향으로 조금씩 흔들어 최소값을 읽는다. 공간이 좁으면 핀 전용 게이지(스냅 게이지)나 짧은 프레임을 쓴다. 조치: 자세 교정 후 재측정. 영향: 불필요한 재가공 또는 오판정. 발생 단계: 황삭 후. 적용 조건: 웨브 사이 크랭크핀 측정. 제외·확인 조건: 없음. 측정기 후보: 대형 외측 마이크로미터, 핀 게이지. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="120" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CS-M-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>크랭크샤프트</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Ø700(-0.08/-0.16)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 편차가 둘 다 음수인 저널 공차를 '700보다 작으면 합격'으로 판정</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널 Ø700(-0.08/-0.16)은 699.840~699.920만 합격인데, 699.950을 '700보다 작다'는 이유로 합격 처리했다. 상한은 699.920이다.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>두 편차가 모두 음수인 공차 해석 오류</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>괄호 안 두 값이 모두 음수면 기준치수보다 작은 쪽 범위만 합격이다. 화면 허용 범위(최소~최대)를 확인한다.</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>대형 외측 마이크로미터, 기준봉</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>틈새 끼워맞춤 저널</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>도면 해석</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>메인 베어링 틈새 부족, 발열·소착</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>허용 범위로 재판정, 재연삭</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 메인 저널, 외경, DIMENSION, Ø700(-0.08/-0.16), 두 편차가 모두 음수인 공차 해석 오류, 메인 저널, C3 도면 해석, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CS-M-038] 부품: 크랭크샤프트. 부위: 메인 저널. 형상: 메인 저널(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø700(-0.08/-0.16). 오류 유형: C3 도면 해석. 중요도: 상. 오류: [정삭] 편차가 둘 다 음수인 저널 공차를 '700보다 작으면 합격'으로 판정. 상황: 메인 저널 Ø700(-0.08/-0.16)은 699.840~699.920만 합격인데, 699.950을 '700보다 작다'는 이유로 합격 처리했다. 상한은 699.920이다. 원인: 두 편차가 모두 음수인 공차 해석 오류. 주의사항: 괄호 안 두 값이 모두 음수면 기준치수보다 작은 쪽 범위만 합격이다. 화면 허용 범위(최소~최대)를 확인한다. 조치: 허용 범위로 재판정, 재연삭. 영향: 메인 베어링 틈새 부족, 발열·소착. 발생 단계: 정삭 후. 적용 조건: 틈새 끼워맞춤 저널. 제외·확인 조건: 없음. 측정기 후보: 대형 외측 마이크로미터, 기준봉. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="120" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CS-M-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>크랭크샤프트</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Ø700(-0.08/-0.16)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 수축 박음 후 최종 연삭 직후 저널 온도를 기록하지 않음</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>조립 후 최종 연삭 직후 저널 표면이 측정실보다 3℃ 높은 상태에서 699.915(합격)로 기록했다. 강은 Ø700에서 3℃당 약 0.024mm 커지므로 식은 뒤 실제 값은 699.891 근처다. 반대로 하한 근처 값이면 식은 뒤 불합격이 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤면 온도 보정 누락</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>저널별로 표면 온도를 함께 기록하고, 2℃ 이상 차이 나면 식힌 뒤 다시 잰다. 긴 크랭크샤프트는 저널마다 온도가 다를 수 있다.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>대형 외측 마이크로미터, 표면 온도계</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>최종 연삭 직후 저널</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>온도 안정 후 측정한 경우 제외</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>온도·환경</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>성적서 값과 실제 치수 차이</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>온도 안정 후 재측정</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 메인 저널, 외경, DIMENSION, Ø700(-0.08/-0.16), 끼워맞춤면 온도 보정 누락, 메인 저널, C9 온도·환경, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CS-M-039] 부품: 크랭크샤프트. 부위: 메인 저널. 형상: 메인 저널(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø700(-0.08/-0.16). 오류 유형: C9 온도·환경. 중요도: 중. 오류: [정삭] 수축 박음 후 최종 연삭 직후 저널 온도를 기록하지 않음. 상황: 조립 후 최종 연삭 직후 저널 표면이 측정실보다 3℃ 높은 상태에서 699.915(합격)로 기록했다. 강은 Ø700에서 3℃당 약 0.024mm 커지므로 식은 뒤 실제 값은 699.891 근처다. 반대로 하한 근처 값이면 식은 뒤 불합격이 될 수 있다. 원인: 끼워맞춤면 온도 보정 누락. 주의사항: 저널별로 표면 온도를 함께 기록하고, 2℃ 이상 차이 나면 식힌 뒤 다시 잰다. 긴 크랭크샤프트는 저널마다 온도가 다를 수 있다. 조치: 온도 안정 후 재측정. 영향: 성적서 값과 실제 치수 차이. 발생 단계: 정삭 후. 적용 조건: 최종 연삭 직후 저널. 제외·확인 조건: 온도 안정 후 측정한 경우 제외. 측정기 후보: 대형 외측 마이크로미터, 표면 온도계. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="120" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CS-M-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>크랭크샤프트</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>R1 (= Ra 0.4)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 저널 연삭면 조도를 원주 방향으로 재서 Ra가 낮게 나옴</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널(R1 = Ra 0.4)을 원주 방향(연삭 줄무늬와 평행)으로 재서 Ra 0.16으로 합격 처리했다. 축 방향으로 다시 재니 Ra 0.48이었다.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>조도 측정 방향 오류</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>원통 연삭면은 줄무늬에 직각인 축 방향으로 촉침을 움직인다. 저널마다 원주 3곳 이상을 잰다.</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>연삭 저널 조도 측정</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>측정 방법</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>메인 베어링 마모 증가</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>축 방향으로 재측정</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 메인 저널, 표면 거칠기, SURFACE_ROUGHNESS, R1 (= Ra 0.4), 조도 측정 방향 오류, 메인 저널, C5 측정 방법, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CS-M-040] 부품: 크랭크샤프트. 부위: 메인 저널. 형상: 메인 저널(SHAFT). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R1 (= Ra 0.4). 오류 유형: C5 측정 방법. 중요도: 상. 오류: [정삭] 저널 연삭면 조도를 원주 방향으로 재서 Ra가 낮게 나옴. 상황: 메인 저널(R1 = Ra 0.4)을 원주 방향(연삭 줄무늬와 평행)으로 재서 Ra 0.16으로 합격 처리했다. 축 방향으로 다시 재니 Ra 0.48이었다. 원인: 조도 측정 방향 오류. 주의사항: 원통 연삭면은 줄무늬에 직각인 축 방향으로 촉침을 움직인다. 저널마다 원주 3곳 이상을 잰다. 조치: 축 방향으로 재측정. 영향: 메인 베어링 마모 증가. 발생 단계: 정삭 후. 적용 조건: 연삭 저널 조도 측정. 제외·확인 조건: 없음. 측정기 후보: 표면조도계. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CS-M-041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>크랭크샤프트</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>R2 (= Ra 0.4)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 수축 박음 후 크랭크핀 표면을 다시 보지 않아 타흔·녹으로 조도 불합격 유출</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀은 크랭크스로 단품에서 Ra 0.4로 마무리됐지만, 수축 박음·운반 중 생긴 타흔과 녹을 확인하지 않고 출하 검사로 넘겼다. 최종 검사에서 Ra 0.9가 나왔다.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>조립 후 표면 재확인 누락</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>수축 박음·최종 가공 뒤 크랭크핀 표면을 다시 눈으로 보고, 의심 부위는 조도를 다시 잰다. 타흔은 위치·크기를 기록한다.</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계, 육안 확인(조명)</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>단품에서 마무리한 면이 조립 공정을 거친 경우</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>크랭크핀</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>부품 상태</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>커넥팅로드 베어링 손상</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>표면 재확인 후 래핑·연마 여부 결정</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 크랭크핀, 표면 거칠기, SURFACE_ROUGHNESS, R2 (= Ra 0.4), 조립 후 표면 재확인 누락, 크랭크핀, C6 부품 상태, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CS-M-041] 부품: 크랭크샤프트. 부위: 크랭크핀. 형상: 크랭크핀(SHAFT). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R2 (= Ra 0.4). 오류 유형: C6 부품 상태. 중요도: 상. 오류: [정삭] 수축 박음 후 크랭크핀 표면을 다시 보지 않아 타흔·녹으로 조도 불합격 유출. 상황: 크랭크핀은 크랭크스로 단품에서 Ra 0.4로 마무리됐지만, 수축 박음·운반 중 생긴 타흔과 녹을 확인하지 않고 출하 검사로 넘겼다. 최종 검사에서 Ra 0.9가 나왔다. 원인: 조립 후 표면 재확인 누락. 주의사항: 수축 박음·최종 가공 뒤 크랭크핀 표면을 다시 눈으로 보고, 의심 부위는 조도를 다시 잰다. 타흔은 위치·크기를 기록한다. 조치: 표면 재확인 후 래핑·연마 여부 결정. 영향: 커넥팅로드 베어링 손상. 발생 단계: 정삭 후. 적용 조건: 단품에서 마무리한 면이 조립 공정을 거친 경우. 제외·확인 조건: 없음. 측정기 후보: 표면조도계, 육안 확인(조명). 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="120" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CS-M-042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>크랭크샤프트</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Ø700(-0.08/-0.16)</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>공정</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>[중삭] 긴 크랭크샤프트 저널 중삭 떨림 자국을 연삭 여유로 지울 수 있다고 보고 넘김</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>수축 박음 후 저널 중삭에서 방진구와 떨어진 저널에 떨림 자국이 생겼는데, 치수가 중삭 목표 범위라 그대로 연삭으로 넘겼다. 연삭 후에도 자국이 남아 R1(Ra 0.4)을 만족하지 못했다.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>중삭 표면 상태 확인 누락</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>저널마다 중삭 후 치수와 함께 떨림 자국을 확인한다. 자국이 있으면 방진구 위치나 절삭 조건을 바꿔 다시 중삭한다.</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>육안·촉감 확인, 대형 외측 마이크로미터</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>연삭으로 마무리하는 저널의 중삭 후</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>공정 추세·시삭</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>중삭 후</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>정삭 후 조도 불합격, 재연삭으로 치수 부족 위험</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>조건 변경 후 재중삭</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 메인 저널, 외경, DIMENSION, Ø700(-0.08/-0.16), 중삭 표면 상태 확인 누락, 메인 저널, C12 공정 추세·시삭, 중삭 후</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CS-M-042] 부품: 크랭크샤프트. 부위: 메인 저널. 형상: 메인 저널(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø700(-0.08/-0.16). 오류 유형: C12 공정 추세·시삭. 중요도: 상. 오류: [중삭] 긴 크랭크샤프트 저널 중삭 떨림 자국을 연삭 여유로 지울 수 있다고 보고 넘김. 상황: 수축 박음 후 저널 중삭에서 방진구와 떨어진 저널에 떨림 자국이 생겼는데, 치수가 중삭 목표 범위라 그대로 연삭으로 넘겼다. 연삭 후에도 자국이 남아 R1(Ra 0.4)을 만족하지 못했다. 원인: 중삭 표면 상태 확인 누락. 주의사항: 저널마다 중삭 후 치수와 함께 떨림 자국을 확인한다. 자국이 있으면 방진구 위치나 절삭 조건을 바꿔 다시 중삭한다. 조치: 조건 변경 후 재중삭. 영향: 정삭 후 조도 불합격, 재연삭으로 치수 부족 위험. 발생 단계: 중삭 후. 적용 조건: 연삭으로 마무리하는 저널의 중삭 후. 제외·확인 조건: 없음. 측정기 후보: 육안·촉감 확인, 대형 외측 마이크로미터. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="120" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>CS-M-043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>크랭크샤프트</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>R1 (= Ra 0.4)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>[공통] 조도 기호 R1·R2를 반지름 치수로 보고 저널·핀 조도를 재지 않음</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>저널 옆 'R1'과 크랭크핀 옆 'R2'를 필렛 반지름으로 보고 R 게이지로 확인만 했다. 표제란 범례상 R1·R2는 모두 Ra 0.4 조도 기호였다.</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>조도 기호와 반지름 치수 혼동</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>이 도면의 R1·R2는 표제란 범례의 조도 기호다. 실제 반지름(R500·R620)과 구분하고, 관리자 검토 화면에서 조도로 분류됐는지 확인한다.</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>조도를 범례 기호(R1, R2)로 표기한 도면</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>실제 반지름 치수(R500·R620)는 제외</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>도면 해석</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V44" s="6" t="inlineStr">
+        <is>
+          <t>가공 공통</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>조도 미측정</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>조도 측정 후 기록 추가</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>OCR은 R1·R2를 반지름 치수로 분류한다</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 메인 저널, 표면 거칠기, SURFACE_ROUGHNESS, R1 (= Ra 0.4), 조도 기호와 반지름 치수 혼동, 메인 저널, C3 도면 해석, 가공 공통</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CS-M-043] 부품: 크랭크샤프트. 부위: 메인 저널. 형상: 메인 저널(SHAFT). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R1 (= Ra 0.4). 오류 유형: C3 도면 해석. 중요도: 중. 오류: [공통] 조도 기호 R1·R2를 반지름 치수로 보고 저널·핀 조도를 재지 않음. 상황: 저널 옆 'R1'과 크랭크핀 옆 'R2'를 필렛 반지름으로 보고 R 게이지로 확인만 했다. 표제란 범례상 R1·R2는 모두 Ra 0.4 조도 기호였다. 원인: 조도 기호와 반지름 치수 혼동. 주의사항: 이 도면의 R1·R2는 표제란 범례의 조도 기호다. 실제 반지름(R500·R620)과 구분하고, 관리자 검토 화면에서 조도로 분류됐는지 확인한다. 조치: 조도 측정 후 기록 추가. 영향: 조도 미측정. 발생 단계: 가공 공통. 적용 조건: 조도를 범례 기호(R1, R2)로 표기한 도면. 제외·확인 조건: 실제 반지름 치수(R500·R620)는 제외. 측정기 후보: 표면조도계. OCR 참고: OCR은 R1·R2를 반지름 치수로 분류한다. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="120" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CS-M-044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>크랭크샤프트</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>외경</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Ø700(-0.08/-0.16)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>[공통] OCR이 공차 부호를 ':'로 읽은 상태에서 판정 범위를 짐작해 기록</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널 공차 (-0.08/-0.16)을 OCR이 (:0.08/-0.16)으로 읽어 허용 범위가 비어 있었는데, 작업자가 '±0.08'로 짐작해 699.950을 합격으로 기록했다.</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>깨진 공차 표기 임의 해석</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>공차가 깨져 허용 범위가 없으면 판정하지 말고 관리자에게 공차 확정을 요청한다. 측정값만 기록해 둔다.</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>대형 외측 마이크로미터</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>OCR이 공차 부호를 못 읽은 치수</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>관리자 확정 후 제외</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>메인 저널</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>기록·판정</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V45" s="6" t="inlineStr">
+        <is>
+          <t>가공 공통</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>잘못된 합격 판정</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>관리자 확정 후 재판정</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>'-' 를 ':' 로 읽는 오인식</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>SHAFT, 메인 저널, 외경, DIMENSION, Ø700(-0.08/-0.16), 깨진 공차 표기 임의 해석, 메인 저널, C7 기록·판정, 가공 공통</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CS-M-044] 부품: 크랭크샤프트. 부위: 메인 저널. 형상: 메인 저널(SHAFT). 측정 특성: 외경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø700(-0.08/-0.16). 오류 유형: C7 기록·판정. 중요도: 중. 오류: [공통] OCR이 공차 부호를 ':'로 읽은 상태에서 판정 범위를 짐작해 기록. 상황: 메인 저널 공차 (-0.08/-0.16)을 OCR이 (:0.08/-0.16)으로 읽어 허용 범위가 비어 있었는데, 작업자가 '±0.08'로 짐작해 699.950을 합격으로 기록했다. 원인: 깨진 공차 표기 임의 해석. 주의사항: 공차가 깨져 허용 범위가 없으면 판정하지 말고 관리자에게 공차 확정을 요청한다. 측정값만 기록해 둔다. 조치: 관리자 확정 후 재판정. 영향: 잘못된 합격 판정. 발생 단계: 가공 공통. 적용 조건: OCR이 공차 부호를 못 읽은 치수. 제외·확인 조건: 관리자 확정 후 제외. 측정기 후보: 대형 외측 마이크로미터. OCR 참고: '-' 를 ':' 로 읽는 오인식. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA35"/>
+  <autoFilter ref="A1:AA45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5181,7 +6519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5784,6 +7122,176 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CS-M-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CS_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[황삭] 크랭크핀 공차 (+0.08/0)을 축이니 − 공차라고 착각해 679.98을 합격 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CS-M-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CS_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[황삭] 크랭크핀 마무리 직후 따뜻한 상태로 끼워맞춤 공차 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CS-M-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CS_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[황삭] 웨브 사이가 좁아 마이크로미터를 비스듬히 대서 핀 지름 과대</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CS-M-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CS_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[정삭] 편차가 둘 다 음수인 저널 공차를 '700보다 작으면 합격'으로 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CS-M-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CS_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[정삭] 수축 박음 후 최종 연삭 직후 저널 온도를 기록하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CS-M-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CS_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[정삭] 저널 연삭면 조도를 원주 방향으로 재서 Ra가 낮게 나옴</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CS-M-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CS_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[정삭] 수축 박음 후 크랭크핀 표면을 다시 보지 않아 타흔·녹으로 조도 불합격 유출</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CS-M-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CS_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[중삭] 긴 크랭크샤프트 저널 중삭 떨림 자국을 연삭 여유로 지울 수 있다고 보고 넘김</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CS-M-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CS_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[공통] 조도 기호 R1·R2를 반지름 치수로 보고 저널·핀 조도를 재지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CS-M-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CS_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[공통] OCR이 공차 부호를 ':'로 읽은 상태에서 판정 범위를 짐작해 기록</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
